--- a/Cowpea_data_final.xlsx
+++ b/Cowpea_data_final.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\temp\resume\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INTEL-OMS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F0AFF9-29A1-4430-9EBE-8ED33087592B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7890" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
   <si>
     <t>Sl.No.</t>
   </si>
@@ -411,15 +411,42 @@
   <si>
     <t>%*mean seedling length</t>
   </si>
+  <si>
+    <t>Number of seeds germinated out of 50</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>Shoot</t>
+  </si>
+  <si>
+    <t>Germination percentage%</t>
+  </si>
+  <si>
+    <t>Seedling length(cm)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -486,6 +513,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -504,10 +537,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -543,14 +577,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -762,22 +805,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AL169"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" style="18" customWidth="1"/>
     <col min="35" max="35" width="27" style="12" customWidth="1"/>
-    <col min="36" max="36" width="18.88671875" style="12" customWidth="1"/>
-    <col min="37" max="37" width="13.44140625" style="12" customWidth="1"/>
+    <col min="36" max="36" width="18.90625" style="12" customWidth="1"/>
+    <col min="37" max="37" width="13.453125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,45 +833,45 @@
       <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="11"/>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="19" t="s">
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
       <c r="V1" s="11"/>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
       <c r="AB1" s="11"/>
-      <c r="AC1" s="19" t="s">
+      <c r="AC1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
       <c r="AH1" s="11"/>
       <c r="AI1" s="11" t="s">
         <v>9</v>
@@ -839,7 +882,7 @@
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
     </row>
-    <row r="2" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -941,7 +984,7 @@
       <c r="AK2" s="11"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1059,7 +1102,7 @@
       <c r="AK3" s="5"/>
       <c r="AL3" s="4"/>
     </row>
-    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1177,7 +1220,7 @@
       <c r="AK4" s="5"/>
       <c r="AL4" s="4"/>
     </row>
-    <row r="5" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1295,7 +1338,7 @@
       <c r="AK5" s="5"/>
       <c r="AL5" s="4"/>
     </row>
-    <row r="6" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1413,7 +1456,7 @@
       <c r="AK6" s="5"/>
       <c r="AL6" s="4"/>
     </row>
-    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1529,7 +1572,7 @@
       <c r="AK7" s="8"/>
       <c r="AL7" s="9"/>
     </row>
-    <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1645,7 +1688,7 @@
       <c r="AK8" s="5"/>
       <c r="AL8" s="9"/>
     </row>
-    <row r="9" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1761,7 +1804,7 @@
       <c r="AK9" s="5"/>
       <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1877,7 +1920,7 @@
       <c r="AK10" s="5"/>
       <c r="AL10" s="4"/>
     </row>
-    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1993,7 +2036,7 @@
       <c r="AK11" s="8"/>
       <c r="AL11" s="9"/>
     </row>
-    <row r="12" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2109,7 +2152,7 @@
       <c r="AK12" s="8"/>
       <c r="AL12" s="9"/>
     </row>
-    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -2225,7 +2268,7 @@
       <c r="AK13" s="8"/>
       <c r="AL13" s="9"/>
     </row>
-    <row r="14" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2341,7 +2384,7 @@
       <c r="AK14" s="5"/>
       <c r="AL14" s="4"/>
     </row>
-    <row r="15" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2457,7 +2500,7 @@
       <c r="AK15" s="5"/>
       <c r="AL15" s="4"/>
     </row>
-    <row r="16" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -2573,7 +2616,7 @@
       <c r="AK16" s="5"/>
       <c r="AL16" s="4"/>
     </row>
-    <row r="17" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2689,7 +2732,7 @@
       <c r="AK17" s="5"/>
       <c r="AL17" s="4"/>
     </row>
-    <row r="18" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2805,7 +2848,7 @@
       <c r="AK18" s="5"/>
       <c r="AL18" s="4"/>
     </row>
-    <row r="19" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2921,7 +2964,7 @@
       <c r="AK19" s="5"/>
       <c r="AL19" s="4"/>
     </row>
-    <row r="20" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -3037,7 +3080,7 @@
       <c r="AK20" s="5"/>
       <c r="AL20" s="4"/>
     </row>
-    <row r="21" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -3153,7 +3196,7 @@
       <c r="AK21" s="5"/>
       <c r="AL21" s="4"/>
     </row>
-    <row r="22" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -3269,7 +3312,7 @@
       <c r="AK22" s="8"/>
       <c r="AL22" s="4"/>
     </row>
-    <row r="23" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -3385,7 +3428,7 @@
       <c r="AK23" s="5"/>
       <c r="AL23" s="4"/>
     </row>
-    <row r="24" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -3501,7 +3544,7 @@
       <c r="AK24" s="5"/>
       <c r="AL24" s="4"/>
     </row>
-    <row r="25" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -3617,7 +3660,7 @@
       <c r="AK25" s="5"/>
       <c r="AL25" s="4"/>
     </row>
-    <row r="26" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3733,7 +3776,7 @@
       <c r="AK26" s="8"/>
       <c r="AL26" s="4"/>
     </row>
-    <row r="27" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3849,7 +3892,7 @@
       <c r="AK27" s="5"/>
       <c r="AL27" s="4"/>
     </row>
-    <row r="28" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -3965,7 +4008,7 @@
       <c r="AK28" s="5"/>
       <c r="AL28" s="4"/>
     </row>
-    <row r="29" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -4081,7 +4124,7 @@
       <c r="AK29" s="5"/>
       <c r="AL29" s="4"/>
     </row>
-    <row r="30" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -4197,7 +4240,7 @@
       <c r="AK30" s="5"/>
       <c r="AL30" s="4"/>
     </row>
-    <row r="31" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -4313,7 +4356,7 @@
       <c r="AK31" s="5"/>
       <c r="AL31" s="4"/>
     </row>
-    <row r="32" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -4429,7 +4472,7 @@
       <c r="AK32" s="5"/>
       <c r="AL32" s="4"/>
     </row>
-    <row r="33" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -4545,7 +4588,7 @@
       <c r="AK33" s="5"/>
       <c r="AL33" s="4"/>
     </row>
-    <row r="34" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -4661,7 +4704,7 @@
       <c r="AK34" s="5"/>
       <c r="AL34" s="4"/>
     </row>
-    <row r="35" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -4777,7 +4820,7 @@
       <c r="AK35" s="5"/>
       <c r="AL35" s="4"/>
     </row>
-    <row r="36" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -4893,7 +4936,7 @@
       <c r="AK36" s="8"/>
       <c r="AL36" s="9"/>
     </row>
-    <row r="37" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -5009,7 +5052,7 @@
       <c r="AK37" s="8"/>
       <c r="AL37" s="4"/>
     </row>
-    <row r="38" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -5125,7 +5168,7 @@
       <c r="AK38" s="5"/>
       <c r="AL38" s="4"/>
     </row>
-    <row r="39" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -5241,7 +5284,7 @@
       <c r="AK39" s="5"/>
       <c r="AL39" s="4"/>
     </row>
-    <row r="40" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -5357,7 +5400,7 @@
       <c r="AK40" s="5"/>
       <c r="AL40" s="9"/>
     </row>
-    <row r="41" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -5473,7 +5516,7 @@
       <c r="AK41" s="5"/>
       <c r="AL41" s="4"/>
     </row>
-    <row r="42" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -5589,7 +5632,7 @@
       <c r="AK42" s="5"/>
       <c r="AL42" s="4"/>
     </row>
-    <row r="43" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -5705,7 +5748,7 @@
       <c r="AK43" s="8"/>
       <c r="AL43" s="9"/>
     </row>
-    <row r="44" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -5821,7 +5864,7 @@
       <c r="AK44" s="8"/>
       <c r="AL44" s="9"/>
     </row>
-    <row r="45" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -5937,7 +5980,7 @@
       <c r="AK45" s="8"/>
       <c r="AL45" s="4"/>
     </row>
-    <row r="46" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -6053,7 +6096,7 @@
       <c r="AK46" s="5"/>
       <c r="AL46" s="4"/>
     </row>
-    <row r="47" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -6169,7 +6212,7 @@
       <c r="AK47" s="5"/>
       <c r="AL47" s="4"/>
     </row>
-    <row r="48" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -6285,7 +6328,7 @@
       <c r="AK48" s="8"/>
       <c r="AL48" s="9"/>
     </row>
-    <row r="49" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -6401,7 +6444,7 @@
       <c r="AK49" s="5"/>
       <c r="AL49" s="4"/>
     </row>
-    <row r="50" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -6517,7 +6560,7 @@
       <c r="AK50" s="5"/>
       <c r="AL50" s="4"/>
     </row>
-    <row r="51" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -6633,7 +6676,7 @@
       <c r="AK51" s="5"/>
       <c r="AL51" s="4"/>
     </row>
-    <row r="52" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -6749,7 +6792,7 @@
       <c r="AK52" s="5"/>
       <c r="AL52" s="4"/>
     </row>
-    <row r="53" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -6865,7 +6908,7 @@
       <c r="AK53" s="5"/>
       <c r="AL53" s="4"/>
     </row>
-    <row r="54" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -6981,7 +7024,7 @@
       <c r="AK54" s="5"/>
       <c r="AL54" s="4"/>
     </row>
-    <row r="55" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -7097,7 +7140,7 @@
       <c r="AK55" s="8"/>
       <c r="AL55" s="4"/>
     </row>
-    <row r="56" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -7213,7 +7256,7 @@
       <c r="AK56" s="5"/>
       <c r="AL56" s="4"/>
     </row>
-    <row r="57" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -7329,7 +7372,7 @@
       <c r="AK57" s="5"/>
       <c r="AL57" s="4"/>
     </row>
-    <row r="58" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -7445,7 +7488,7 @@
       <c r="AK58" s="8"/>
       <c r="AL58" s="9"/>
     </row>
-    <row r="59" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -7561,7 +7604,7 @@
       <c r="AK59" s="5"/>
       <c r="AL59" s="4"/>
     </row>
-    <row r="60" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -7677,7 +7720,7 @@
       <c r="AK60" s="8"/>
       <c r="AL60" s="9"/>
     </row>
-    <row r="61" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -7793,7 +7836,7 @@
       <c r="AK61" s="5"/>
       <c r="AL61" s="4"/>
     </row>
-    <row r="62" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -7909,7 +7952,7 @@
       <c r="AK62" s="5"/>
       <c r="AL62" s="4"/>
     </row>
-    <row r="63" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -8025,7 +8068,7 @@
       <c r="AK63" s="5"/>
       <c r="AL63" s="4"/>
     </row>
-    <row r="64" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -8141,7 +8184,7 @@
       <c r="AK64" s="5"/>
       <c r="AL64" s="4"/>
     </row>
-    <row r="65" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -8257,7 +8300,7 @@
       <c r="AK65" s="8"/>
       <c r="AL65" s="9"/>
     </row>
-    <row r="66" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -8373,7 +8416,7 @@
       <c r="AK66" s="5"/>
       <c r="AL66" s="4"/>
     </row>
-    <row r="67" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -8489,7 +8532,7 @@
       <c r="AK67" s="5"/>
       <c r="AL67" s="4"/>
     </row>
-    <row r="68" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -8605,7 +8648,7 @@
       <c r="AK68" s="5"/>
       <c r="AL68" s="4"/>
     </row>
-    <row r="69" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -8721,7 +8764,7 @@
       <c r="AK69" s="5"/>
       <c r="AL69" s="4"/>
     </row>
-    <row r="70" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -8837,7 +8880,7 @@
       <c r="AK70" s="5"/>
       <c r="AL70" s="4"/>
     </row>
-    <row r="71" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -8953,7 +8996,7 @@
       <c r="AK71" s="5"/>
       <c r="AL71" s="4"/>
     </row>
-    <row r="72" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -9069,7 +9112,7 @@
       <c r="AK72" s="8"/>
       <c r="AL72" s="4"/>
     </row>
-    <row r="73" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -9185,7 +9228,7 @@
       <c r="AK73" s="5"/>
       <c r="AL73" s="4"/>
     </row>
-    <row r="74" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -9301,7 +9344,7 @@
       <c r="AK74" s="5"/>
       <c r="AL74" s="4"/>
     </row>
-    <row r="75" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -9417,7 +9460,7 @@
       <c r="AK75" s="8"/>
       <c r="AL75" s="9"/>
     </row>
-    <row r="76" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -9533,7 +9576,7 @@
       <c r="AK76" s="8"/>
       <c r="AL76" s="9"/>
     </row>
-    <row r="77" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -9649,7 +9692,7 @@
       <c r="AK77" s="5"/>
       <c r="AL77" s="4"/>
     </row>
-    <row r="78" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -9765,7 +9808,7 @@
       <c r="AK78" s="5"/>
       <c r="AL78" s="9"/>
     </row>
-    <row r="79" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -9881,7 +9924,7 @@
       <c r="AK79" s="8"/>
       <c r="AL79" s="9"/>
     </row>
-    <row r="80" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -9997,7 +10040,7 @@
       <c r="AK80" s="8"/>
       <c r="AL80" s="9"/>
     </row>
-    <row r="81" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -10113,7 +10156,7 @@
       <c r="AK81" s="5"/>
       <c r="AL81" s="4"/>
     </row>
-    <row r="82" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -10229,7 +10272,7 @@
       <c r="AK82" s="5"/>
       <c r="AL82" s="4"/>
     </row>
-    <row r="83" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -10345,7 +10388,7 @@
       <c r="AK83" s="5"/>
       <c r="AL83" s="4"/>
     </row>
-    <row r="84" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -10461,7 +10504,7 @@
       <c r="AK84" s="5"/>
       <c r="AL84" s="4"/>
     </row>
-    <row r="85" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -10577,7 +10620,7 @@
       <c r="AK85" s="5"/>
       <c r="AL85" s="4"/>
     </row>
-    <row r="86" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -10693,7 +10736,7 @@
       <c r="AK86" s="5"/>
       <c r="AL86" s="4"/>
     </row>
-    <row r="87" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -10809,7 +10852,7 @@
       <c r="AK87" s="5"/>
       <c r="AL87" s="4"/>
     </row>
-    <row r="88" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -10925,7 +10968,7 @@
       <c r="AK88" s="5"/>
       <c r="AL88" s="4"/>
     </row>
-    <row r="89" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -11041,7 +11084,7 @@
       <c r="AK89" s="5"/>
       <c r="AL89" s="4"/>
     </row>
-    <row r="90" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -11157,7 +11200,7 @@
       <c r="AK90" s="5"/>
       <c r="AL90" s="4"/>
     </row>
-    <row r="91" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -11273,7 +11316,7 @@
       <c r="AK91" s="5"/>
       <c r="AL91" s="4"/>
     </row>
-    <row r="92" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -11389,7 +11432,7 @@
       <c r="AK92" s="8"/>
       <c r="AL92" s="9"/>
     </row>
-    <row r="93" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -11505,7 +11548,7 @@
       <c r="AK93" s="5"/>
       <c r="AL93" s="4"/>
     </row>
-    <row r="94" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -11621,7 +11664,7 @@
       <c r="AK94" s="5"/>
       <c r="AL94" s="4"/>
     </row>
-    <row r="95" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -11737,7 +11780,7 @@
       <c r="AK95" s="5"/>
       <c r="AL95" s="4"/>
     </row>
-    <row r="96" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -11853,7 +11896,7 @@
       <c r="AK96" s="5"/>
       <c r="AL96" s="4"/>
     </row>
-    <row r="97" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -11969,7 +12012,7 @@
       <c r="AK97" s="5"/>
       <c r="AL97" s="4"/>
     </row>
-    <row r="98" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -12085,7 +12128,7 @@
       <c r="AK98" s="8"/>
       <c r="AL98" s="9"/>
     </row>
-    <row r="99" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -12201,7 +12244,7 @@
       <c r="AK99" s="8"/>
       <c r="AL99" s="9"/>
     </row>
-    <row r="100" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -12317,7 +12360,7 @@
       <c r="AK100" s="5"/>
       <c r="AL100" s="9"/>
     </row>
-    <row r="101" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -12433,7 +12476,7 @@
       <c r="AK101" s="5"/>
       <c r="AL101" s="4"/>
     </row>
-    <row r="102" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -12549,7 +12592,7 @@
       <c r="AK102" s="5"/>
       <c r="AL102" s="4"/>
     </row>
-    <row r="103" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -12665,7 +12708,7 @@
       <c r="AK103" s="5"/>
       <c r="AL103" s="4"/>
     </row>
-    <row r="104" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -12779,7 +12822,7 @@
       <c r="AK104" s="5"/>
       <c r="AL104" s="11"/>
     </row>
-    <row r="105" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -12895,7 +12938,7 @@
       <c r="AK105" s="8"/>
       <c r="AL105" s="9"/>
     </row>
-    <row r="106" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -13011,7 +13054,7 @@
       <c r="AK106" s="5"/>
       <c r="AL106" s="4"/>
     </row>
-    <row r="107" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -13127,7 +13170,7 @@
       <c r="AK107" s="5"/>
       <c r="AL107" s="4"/>
     </row>
-    <row r="108" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -13243,7 +13286,7 @@
       <c r="AK108" s="5"/>
       <c r="AL108" s="4"/>
     </row>
-    <row r="109" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -13359,7 +13402,7 @@
       <c r="AK109" s="8"/>
       <c r="AL109" s="9"/>
     </row>
-    <row r="110" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -13475,7 +13518,7 @@
       <c r="AK110" s="5"/>
       <c r="AL110" s="4"/>
     </row>
-    <row r="111" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -13591,7 +13634,7 @@
       <c r="AK111" s="5"/>
       <c r="AL111" s="4"/>
     </row>
-    <row r="112" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -13707,7 +13750,7 @@
       <c r="AK112" s="5"/>
       <c r="AL112" s="4"/>
     </row>
-    <row r="113" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -13823,7 +13866,7 @@
       <c r="AK113" s="5"/>
       <c r="AL113" s="4"/>
     </row>
-    <row r="114" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -13939,7 +13982,7 @@
       <c r="AK114" s="5"/>
       <c r="AL114" s="4"/>
     </row>
-    <row r="115" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -14055,7 +14098,7 @@
       <c r="AK115" s="5"/>
       <c r="AL115" s="4"/>
     </row>
-    <row r="116" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>114</v>
       </c>
@@ -14171,7 +14214,7 @@
       <c r="AK116" s="8"/>
       <c r="AL116" s="9"/>
     </row>
-    <row r="117" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>115</v>
       </c>
@@ -14287,7 +14330,7 @@
       <c r="AK117" s="5"/>
       <c r="AL117" s="4"/>
     </row>
-    <row r="118" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>116</v>
       </c>
@@ -14403,7 +14446,7 @@
       <c r="AK118" s="5"/>
       <c r="AL118" s="4"/>
     </row>
-    <row r="119" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>117</v>
       </c>
@@ -14519,7 +14562,7 @@
       <c r="AK119" s="5"/>
       <c r="AL119" s="4"/>
     </row>
-    <row r="120" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>118</v>
       </c>
@@ -14635,7 +14678,7 @@
       <c r="AK120" s="5"/>
       <c r="AL120" s="4"/>
     </row>
-    <row r="121" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>119</v>
       </c>
@@ -14751,7 +14794,7 @@
       <c r="AK121" s="5"/>
       <c r="AL121" s="4"/>
     </row>
-    <row r="122" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>120</v>
       </c>
@@ -14867,7 +14910,7 @@
       <c r="AK122" s="8"/>
       <c r="AL122" s="9"/>
     </row>
-    <row r="123" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>121</v>
       </c>
@@ -14983,7 +15026,7 @@
       <c r="AK123" s="8"/>
       <c r="AL123" s="9"/>
     </row>
-    <row r="124" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>122</v>
       </c>
@@ -15099,7 +15142,7 @@
       <c r="AK124" s="5"/>
       <c r="AL124" s="4"/>
     </row>
-    <row r="125" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>123</v>
       </c>
@@ -15213,7 +15256,7 @@
       <c r="AK125" s="5"/>
       <c r="AL125" s="4"/>
     </row>
-    <row r="126" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>124</v>
       </c>
@@ -15327,7 +15370,7 @@
       <c r="AK126" s="5"/>
       <c r="AL126" s="4"/>
     </row>
-    <row r="127" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>125</v>
       </c>
@@ -15441,7 +15484,7 @@
       <c r="AK127" s="5"/>
       <c r="AL127" s="4"/>
     </row>
-    <row r="128" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>126</v>
       </c>
@@ -15555,7 +15598,7 @@
       <c r="AK128" s="5"/>
       <c r="AL128" s="4"/>
     </row>
-    <row r="129" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>127</v>
       </c>
@@ -15669,7 +15712,7 @@
       <c r="AK129" s="5"/>
       <c r="AL129" s="9"/>
     </row>
-    <row r="130" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>128</v>
       </c>
@@ -15785,7 +15828,7 @@
       <c r="AK130" s="8"/>
       <c r="AL130" s="9"/>
     </row>
-    <row r="131" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>129</v>
       </c>
@@ -15812,7 +15855,7 @@
         <v>65.099999999999994</v>
       </c>
       <c r="J131" s="6">
-        <f t="shared" ref="J131:J162" si="24">AVERAGE(E131:I131)</f>
+        <f t="shared" ref="J131:J134" si="24">AVERAGE(E131:I131)</f>
         <v>59.98</v>
       </c>
       <c r="K131" s="6">
@@ -15831,7 +15874,7 @@
         <v>8</v>
       </c>
       <c r="P131" s="6">
-        <f t="shared" ref="P131:P162" si="25">AVERAGE(K131:O131)</f>
+        <f t="shared" ref="P131:P134" si="25">AVERAGE(K131:O131)</f>
         <v>8</v>
       </c>
       <c r="Q131" s="6">
@@ -15850,7 +15893,7 @@
         <v>12</v>
       </c>
       <c r="V131" s="3">
-        <f t="shared" ref="V131:V162" si="26">AVERAGE(Q131:U131)</f>
+        <f t="shared" ref="V131:V134" si="26">AVERAGE(Q131:U131)</f>
         <v>12.8</v>
       </c>
       <c r="W131" s="6">
@@ -15869,7 +15912,7 @@
         <v>17</v>
       </c>
       <c r="AB131" s="3">
-        <f t="shared" ref="AB131:AB162" si="27">AVERAGE(W131:AA131)</f>
+        <f t="shared" ref="AB131:AB134" si="27">AVERAGE(W131:AA131)</f>
         <v>16.8</v>
       </c>
       <c r="AC131" s="6">
@@ -15888,20 +15931,20 @@
         <v>14.5</v>
       </c>
       <c r="AH131" s="3">
-        <f t="shared" ref="AH131:AH162" si="28">AVERAGE(AC131:AG131)</f>
+        <f t="shared" ref="AH131:AH134" si="28">AVERAGE(AC131:AG131)</f>
         <v>14.6</v>
       </c>
       <c r="AI131" s="7">
         <v>59.42</v>
       </c>
       <c r="AJ131" s="4">
-        <f t="shared" ref="AJ131:AJ162" si="29">AI131*7407.4/1000</f>
+        <f t="shared" ref="AJ131:AJ134" si="29">AI131*7407.4/1000</f>
         <v>440.14770799999997</v>
       </c>
       <c r="AK131" s="5"/>
       <c r="AL131" s="4"/>
     </row>
-    <row r="132" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>130</v>
       </c>
@@ -16017,7 +16060,7 @@
       <c r="AK132" s="5"/>
       <c r="AL132" s="4"/>
     </row>
-    <row r="133" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>131</v>
       </c>
@@ -16133,7 +16176,7 @@
       <c r="AK133" s="5"/>
       <c r="AL133" s="4"/>
     </row>
-    <row r="134" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>132</v>
       </c>
@@ -16249,7 +16292,7 @@
       <c r="AK134" s="5"/>
       <c r="AL134" s="4"/>
     </row>
-    <row r="136" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -16289,7 +16332,7 @@
       <c r="AK136" s="2"/>
       <c r="AL136" s="9"/>
     </row>
-    <row r="137" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -16329,7 +16372,7 @@
       <c r="AK137" s="2"/>
       <c r="AL137" s="2"/>
     </row>
-    <row r="138" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -16369,97 +16412,97 @@
       <c r="AK138" s="2"/>
       <c r="AL138" s="2"/>
     </row>
-    <row r="139" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ139" s="11"/>
     </row>
-    <row r="140" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ140" s="11"/>
     </row>
-    <row r="141" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ141" s="11"/>
     </row>
-    <row r="142" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ142" s="11"/>
     </row>
-    <row r="143" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ143" s="11"/>
     </row>
-    <row r="144" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ144" s="11"/>
     </row>
-    <row r="145" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ145" s="11"/>
     </row>
-    <row r="146" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ146" s="11"/>
     </row>
-    <row r="147" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ147" s="11"/>
     </row>
-    <row r="148" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ148" s="11"/>
     </row>
-    <row r="149" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ149" s="11"/>
     </row>
-    <row r="150" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ150" s="11"/>
     </row>
-    <row r="151" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ151" s="11"/>
     </row>
-    <row r="152" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ152" s="11"/>
     </row>
-    <row r="153" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ153" s="11"/>
     </row>
-    <row r="154" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ154" s="11"/>
     </row>
-    <row r="155" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ155" s="11"/>
     </row>
-    <row r="156" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ156" s="11"/>
     </row>
-    <row r="157" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ157" s="11"/>
     </row>
-    <row r="158" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ158" s="11"/>
     </row>
-    <row r="159" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ159" s="11"/>
     </row>
-    <row r="160" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ160" s="11"/>
     </row>
-    <row r="161" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ161" s="11"/>
     </row>
-    <row r="162" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ162" s="11"/>
     </row>
-    <row r="163" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ163" s="11"/>
     </row>
-    <row r="164" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ164" s="11"/>
     </row>
-    <row r="165" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ165" s="11"/>
     </row>
-    <row r="166" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ166" s="11"/>
     </row>
-    <row r="167" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ167" s="11"/>
     </row>
-    <row r="168" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ168" s="11"/>
     </row>
-    <row r="169" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AJ169" s="11"/>
     </row>
   </sheetData>
@@ -16471,45 +16514,2204 @@
     <mergeCell ref="W1:AA1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>46</v>
+      </c>
+      <c r="E4" s="21">
+        <f>AVERAGE(B4:D4)</f>
+        <v>44.333333333333336</v>
+      </c>
+      <c r="F4" s="21">
+        <f>E4/50*100</f>
+        <v>88.666666666666671</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>48</v>
+      </c>
+      <c r="D5">
+        <v>49</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" ref="E5:E18" si="0">AVERAGE(B5:D5)</f>
+        <v>49</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" ref="F5:F18" si="1">E5/50*100</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>46</v>
+      </c>
+      <c r="E6" s="21">
+        <f t="shared" si="0"/>
+        <v>44.333333333333336</v>
+      </c>
+      <c r="F6" s="21">
+        <f t="shared" si="1"/>
+        <v>88.666666666666671</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>44</v>
+      </c>
+      <c r="D7">
+        <v>46</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8" s="21">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>47</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="0"/>
+        <v>45.666666666666664</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="1"/>
+        <v>91.333333333333329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <v>48</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+      <c r="E10" s="21">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="F10" s="21">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>45</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>45</v>
+      </c>
+      <c r="D11">
+        <v>44</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="0"/>
+        <v>43.333333333333336</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="1"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>46</v>
+      </c>
+      <c r="C12">
+        <v>48</v>
+      </c>
+      <c r="D12">
+        <v>47</v>
+      </c>
+      <c r="E12" s="21">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="F12" s="21">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>49</v>
+      </c>
+      <c r="B13">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>46</v>
+      </c>
+      <c r="D13">
+        <v>48</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <v>47</v>
+      </c>
+      <c r="C14">
+        <v>48</v>
+      </c>
+      <c r="D14">
+        <v>47</v>
+      </c>
+      <c r="E14" s="21">
+        <f t="shared" si="0"/>
+        <v>47.333333333333336</v>
+      </c>
+      <c r="F14" s="21">
+        <f t="shared" si="1"/>
+        <v>94.666666666666671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>58</v>
+      </c>
+      <c r="B15">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>49</v>
+      </c>
+      <c r="D15">
+        <v>48</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="0"/>
+        <v>48.333333333333336</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="1"/>
+        <v>96.666666666666671</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>78</v>
+      </c>
+      <c r="B16">
+        <v>46</v>
+      </c>
+      <c r="C16">
+        <v>44</v>
+      </c>
+      <c r="D16">
+        <v>46</v>
+      </c>
+      <c r="E16" s="21">
+        <f t="shared" si="0"/>
+        <v>45.333333333333336</v>
+      </c>
+      <c r="F16" s="21">
+        <f t="shared" si="1"/>
+        <v>90.666666666666671</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>89</v>
+      </c>
+      <c r="B17">
+        <v>45</v>
+      </c>
+      <c r="C17">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>47</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="0"/>
+        <v>44.666666666666664</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="1"/>
+        <v>89.333333333333329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>112</v>
+      </c>
+      <c r="B18">
+        <v>43</v>
+      </c>
+      <c r="C18">
+        <v>47</v>
+      </c>
+      <c r="D18">
+        <v>46</v>
+      </c>
+      <c r="E18" s="21">
+        <f t="shared" si="0"/>
+        <v>45.333333333333336</v>
+      </c>
+      <c r="F18" s="21">
+        <f t="shared" si="1"/>
+        <v>90.666666666666671</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AP33"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B2" s="19"/>
+      <c r="C2" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B3" s="19"/>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>9</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3" s="19">
+        <v>1</v>
+      </c>
+      <c r="N3" s="19">
+        <v>2</v>
+      </c>
+      <c r="O3" s="19">
+        <v>3</v>
+      </c>
+      <c r="P3" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>5</v>
+      </c>
+      <c r="R3" s="19">
+        <v>6</v>
+      </c>
+      <c r="S3" s="19">
+        <v>7</v>
+      </c>
+      <c r="T3" s="19">
+        <v>8</v>
+      </c>
+      <c r="U3" s="19">
+        <v>9</v>
+      </c>
+      <c r="V3" s="19">
+        <v>10</v>
+      </c>
+      <c r="W3" s="19">
+        <v>1</v>
+      </c>
+      <c r="X3" s="19">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="19">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="19">
+        <v>5</v>
+      </c>
+      <c r="AB3" s="19">
+        <v>6</v>
+      </c>
+      <c r="AC3" s="19">
+        <v>7</v>
+      </c>
+      <c r="AD3" s="19">
+        <v>8</v>
+      </c>
+      <c r="AE3" s="19">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="19">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="19"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="19">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>15.5</v>
+      </c>
+      <c r="D4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>14</v>
+      </c>
+      <c r="M4">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>14.7</v>
+      </c>
+      <c r="O4">
+        <v>12.9</v>
+      </c>
+      <c r="P4">
+        <v>20</v>
+      </c>
+      <c r="Q4">
+        <v>14.5</v>
+      </c>
+      <c r="W4">
+        <v>14.8</v>
+      </c>
+      <c r="X4">
+        <v>15.9</v>
+      </c>
+      <c r="Y4">
+        <v>16.2</v>
+      </c>
+      <c r="Z4">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AA4">
+        <v>14.6</v>
+      </c>
+      <c r="AH4" s="20"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5">
+        <v>11.6</v>
+      </c>
+      <c r="D5">
+        <v>11.5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>11.5</v>
+      </c>
+      <c r="G5">
+        <v>13.5</v>
+      </c>
+      <c r="M5">
+        <v>12.5</v>
+      </c>
+      <c r="N5">
+        <v>12.4</v>
+      </c>
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>11.4</v>
+      </c>
+      <c r="Q5">
+        <v>14.1</v>
+      </c>
+      <c r="W5">
+        <v>11.8</v>
+      </c>
+      <c r="X5">
+        <v>11.2</v>
+      </c>
+      <c r="Y5">
+        <v>9.5</v>
+      </c>
+      <c r="Z5">
+        <v>12</v>
+      </c>
+      <c r="AA5">
+        <v>13.8</v>
+      </c>
+      <c r="AH5" s="20"/>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="19">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>17</v>
+      </c>
+      <c r="P6">
+        <v>9</v>
+      </c>
+      <c r="Q6">
+        <v>14</v>
+      </c>
+      <c r="W6">
+        <v>15</v>
+      </c>
+      <c r="X6">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="Y6">
+        <v>18</v>
+      </c>
+      <c r="Z6">
+        <v>22</v>
+      </c>
+      <c r="AA6">
+        <v>16.3</v>
+      </c>
+      <c r="AH6" s="20"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>14</v>
+      </c>
+      <c r="O7">
+        <v>13</v>
+      </c>
+      <c r="P7">
+        <v>14</v>
+      </c>
+      <c r="Q7">
+        <v>12</v>
+      </c>
+      <c r="W7">
+        <v>11</v>
+      </c>
+      <c r="X7">
+        <v>9.5</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>13</v>
+      </c>
+      <c r="AA7">
+        <v>13</v>
+      </c>
+      <c r="AH7" s="20"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="19">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>15.5</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>14.4</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="M8">
+        <v>22</v>
+      </c>
+      <c r="N8">
+        <v>13.5</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+      <c r="P8">
+        <v>19.5</v>
+      </c>
+      <c r="Q8">
+        <v>14.2</v>
+      </c>
+      <c r="W8">
+        <v>16</v>
+      </c>
+      <c r="X8">
+        <v>17.5</v>
+      </c>
+      <c r="Y8">
+        <v>15</v>
+      </c>
+      <c r="Z8">
+        <v>18.5</v>
+      </c>
+      <c r="AA8">
+        <v>13</v>
+      </c>
+      <c r="AH8" s="20"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9">
+        <v>11.5</v>
+      </c>
+      <c r="D9">
+        <v>14.4</v>
+      </c>
+      <c r="E9">
+        <v>14.3</v>
+      </c>
+      <c r="F9">
+        <v>15.7</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="M9">
+        <v>11.4</v>
+      </c>
+      <c r="N9">
+        <v>16</v>
+      </c>
+      <c r="O9">
+        <v>15.3</v>
+      </c>
+      <c r="P9">
+        <v>12</v>
+      </c>
+      <c r="Q9">
+        <v>13.5</v>
+      </c>
+      <c r="W9">
+        <v>12</v>
+      </c>
+      <c r="X9">
+        <v>15</v>
+      </c>
+      <c r="Y9">
+        <v>14.8</v>
+      </c>
+      <c r="Z9">
+        <v>15</v>
+      </c>
+      <c r="AA9">
+        <v>14</v>
+      </c>
+      <c r="AH9" s="20"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="19">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G10">
+        <v>15.2</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>12.6</v>
+      </c>
+      <c r="O10">
+        <v>17.5</v>
+      </c>
+      <c r="P10">
+        <v>17.3</v>
+      </c>
+      <c r="Q10">
+        <v>12</v>
+      </c>
+      <c r="W10">
+        <v>19</v>
+      </c>
+      <c r="X10">
+        <v>17</v>
+      </c>
+      <c r="Y10">
+        <v>18</v>
+      </c>
+      <c r="Z10">
+        <v>16</v>
+      </c>
+      <c r="AA10">
+        <v>14</v>
+      </c>
+      <c r="AH10" s="20"/>
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>11.5</v>
+      </c>
+      <c r="G11">
+        <v>13.4</v>
+      </c>
+      <c r="M11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N11">
+        <v>14.5</v>
+      </c>
+      <c r="O11">
+        <v>10.7</v>
+      </c>
+      <c r="P11">
+        <v>15.5</v>
+      </c>
+      <c r="Q11">
+        <v>13.5</v>
+      </c>
+      <c r="W11">
+        <v>11</v>
+      </c>
+      <c r="X11">
+        <v>12.5</v>
+      </c>
+      <c r="Y11">
+        <v>11</v>
+      </c>
+      <c r="Z11">
+        <v>13</v>
+      </c>
+      <c r="AA11">
+        <v>12</v>
+      </c>
+      <c r="AH11" s="20"/>
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="19">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>17.5</v>
+      </c>
+      <c r="D12">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E12">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>22.3</v>
+      </c>
+      <c r="M12">
+        <v>21</v>
+      </c>
+      <c r="N12">
+        <v>17.3</v>
+      </c>
+      <c r="O12">
+        <v>15</v>
+      </c>
+      <c r="P12">
+        <v>15</v>
+      </c>
+      <c r="Q12">
+        <v>12</v>
+      </c>
+      <c r="W12">
+        <v>18</v>
+      </c>
+      <c r="X12">
+        <v>18.5</v>
+      </c>
+      <c r="Y12">
+        <v>17</v>
+      </c>
+      <c r="Z12">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AA12">
+        <v>20</v>
+      </c>
+      <c r="AH12" s="20"/>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>13.2</v>
+      </c>
+      <c r="E13">
+        <v>16</v>
+      </c>
+      <c r="F13">
+        <v>12.5</v>
+      </c>
+      <c r="G13">
+        <v>15.5</v>
+      </c>
+      <c r="M13">
+        <v>21</v>
+      </c>
+      <c r="N13">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>15.4</v>
+      </c>
+      <c r="P13">
+        <v>16</v>
+      </c>
+      <c r="Q13">
+        <v>11.5</v>
+      </c>
+      <c r="W13">
+        <v>15</v>
+      </c>
+      <c r="X13">
+        <v>14.5</v>
+      </c>
+      <c r="Y13">
+        <v>15.8</v>
+      </c>
+      <c r="Z13">
+        <v>13.5</v>
+      </c>
+      <c r="AA13">
+        <v>12</v>
+      </c>
+      <c r="AH13" s="20"/>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="19">
+        <v>36</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="M14">
+        <v>17.7</v>
+      </c>
+      <c r="N14">
+        <v>13.5</v>
+      </c>
+      <c r="O14">
+        <v>23</v>
+      </c>
+      <c r="P14">
+        <v>15.4</v>
+      </c>
+      <c r="Q14">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="W14">
+        <v>7</v>
+      </c>
+      <c r="X14">
+        <v>12</v>
+      </c>
+      <c r="Y14">
+        <v>14</v>
+      </c>
+      <c r="Z14">
+        <v>12</v>
+      </c>
+      <c r="AA14">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="20"/>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
+      </c>
+      <c r="M15">
+        <v>11.5</v>
+      </c>
+      <c r="N15">
+        <v>14.2</v>
+      </c>
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15">
+        <v>14.5</v>
+      </c>
+      <c r="Q15">
+        <v>12.5</v>
+      </c>
+      <c r="W15">
+        <v>13</v>
+      </c>
+      <c r="X15">
+        <v>13.5</v>
+      </c>
+      <c r="Y15">
+        <v>14</v>
+      </c>
+      <c r="Z15">
+        <v>13</v>
+      </c>
+      <c r="AA15">
+        <v>12</v>
+      </c>
+      <c r="AH15" s="20"/>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="19">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>17.5</v>
+      </c>
+      <c r="E16">
+        <v>15.2</v>
+      </c>
+      <c r="F16">
+        <v>23.5</v>
+      </c>
+      <c r="G16">
+        <v>15.5</v>
+      </c>
+      <c r="M16">
+        <v>16.5</v>
+      </c>
+      <c r="N16">
+        <v>21</v>
+      </c>
+      <c r="O16">
+        <v>15.5</v>
+      </c>
+      <c r="P16">
+        <v>15.7</v>
+      </c>
+      <c r="Q16">
+        <v>13.7</v>
+      </c>
+      <c r="W16">
+        <v>17</v>
+      </c>
+      <c r="X16">
+        <v>18</v>
+      </c>
+      <c r="Y16">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Z16">
+        <v>22</v>
+      </c>
+      <c r="AA16">
+        <v>14.3</v>
+      </c>
+      <c r="AH16" s="20"/>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17">
+        <v>17.5</v>
+      </c>
+      <c r="D17">
+        <v>19</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>13.5</v>
+      </c>
+      <c r="G17">
+        <v>12.8</v>
+      </c>
+      <c r="M17">
+        <v>11.4</v>
+      </c>
+      <c r="N17">
+        <v>11.5</v>
+      </c>
+      <c r="O17">
+        <v>14.5</v>
+      </c>
+      <c r="P17">
+        <v>17.5</v>
+      </c>
+      <c r="Q17">
+        <v>11.5</v>
+      </c>
+      <c r="W17">
+        <v>16</v>
+      </c>
+      <c r="X17">
+        <v>17</v>
+      </c>
+      <c r="Y17">
+        <v>14</v>
+      </c>
+      <c r="Z17">
+        <v>15</v>
+      </c>
+      <c r="AA17">
+        <v>13</v>
+      </c>
+      <c r="AH17" s="20"/>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="19">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>11.5</v>
+      </c>
+      <c r="D18">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E18">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>14.5</v>
+      </c>
+      <c r="G18">
+        <v>21</v>
+      </c>
+      <c r="M18">
+        <v>17.5</v>
+      </c>
+      <c r="N18">
+        <v>10</v>
+      </c>
+      <c r="O18">
+        <v>22.5</v>
+      </c>
+      <c r="P18">
+        <v>13.5</v>
+      </c>
+      <c r="Q18">
+        <v>12.5</v>
+      </c>
+      <c r="W18">
+        <v>12</v>
+      </c>
+      <c r="X18">
+        <v>17</v>
+      </c>
+      <c r="Y18">
+        <v>13</v>
+      </c>
+      <c r="Z18">
+        <v>15</v>
+      </c>
+      <c r="AA18">
+        <v>19</v>
+      </c>
+      <c r="AH18" s="20"/>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>13.4</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>15</v>
+      </c>
+      <c r="O19">
+        <v>9</v>
+      </c>
+      <c r="P19">
+        <v>14.5</v>
+      </c>
+      <c r="Q19">
+        <v>16.5</v>
+      </c>
+      <c r="W19">
+        <v>16</v>
+      </c>
+      <c r="X19">
+        <v>15</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>15</v>
+      </c>
+      <c r="AA19">
+        <v>15</v>
+      </c>
+      <c r="AH19" s="20"/>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="19">
+        <v>48</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="G20">
+        <v>15</v>
+      </c>
+      <c r="M20">
+        <v>21</v>
+      </c>
+      <c r="N20">
+        <v>16</v>
+      </c>
+      <c r="O20">
+        <v>12</v>
+      </c>
+      <c r="P20">
+        <v>17</v>
+      </c>
+      <c r="Q20">
+        <v>14</v>
+      </c>
+      <c r="W20">
+        <v>19.2</v>
+      </c>
+      <c r="X20">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="Y20">
+        <v>15</v>
+      </c>
+      <c r="Z20">
+        <v>18</v>
+      </c>
+      <c r="AA20">
+        <v>14</v>
+      </c>
+      <c r="AH20" s="20"/>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <v>15</v>
+      </c>
+      <c r="N21">
+        <v>11</v>
+      </c>
+      <c r="O21">
+        <v>13</v>
+      </c>
+      <c r="P21">
+        <v>11</v>
+      </c>
+      <c r="Q21">
+        <v>13</v>
+      </c>
+      <c r="W21">
+        <v>11</v>
+      </c>
+      <c r="X21">
+        <v>12</v>
+      </c>
+      <c r="Y21">
+        <v>13</v>
+      </c>
+      <c r="Z21">
+        <v>12</v>
+      </c>
+      <c r="AA21">
+        <v>12</v>
+      </c>
+      <c r="AH21" s="20"/>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="19">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>17</v>
+      </c>
+      <c r="D22">
+        <v>16</v>
+      </c>
+      <c r="E22">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F22">
+        <v>13.5</v>
+      </c>
+      <c r="G22">
+        <v>21.4</v>
+      </c>
+      <c r="M22">
+        <v>22</v>
+      </c>
+      <c r="N22">
+        <v>20.5</v>
+      </c>
+      <c r="O22">
+        <v>10.7</v>
+      </c>
+      <c r="P22">
+        <v>20.2</v>
+      </c>
+      <c r="Q22">
+        <v>19.3</v>
+      </c>
+      <c r="W22">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="X22">
+        <v>19</v>
+      </c>
+      <c r="Y22">
+        <v>12</v>
+      </c>
+      <c r="Z22">
+        <v>18.3</v>
+      </c>
+      <c r="AA22">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="AH22" s="20"/>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23">
+        <v>14.4</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>13.5</v>
+      </c>
+      <c r="F23">
+        <v>13.5</v>
+      </c>
+      <c r="G23">
+        <v>10.5</v>
+      </c>
+      <c r="M23">
+        <v>14.8</v>
+      </c>
+      <c r="N23">
+        <v>11.5</v>
+      </c>
+      <c r="O23">
+        <v>13.5</v>
+      </c>
+      <c r="P23">
+        <v>13.3</v>
+      </c>
+      <c r="Q23">
+        <v>14.2</v>
+      </c>
+      <c r="W23">
+        <v>13.4</v>
+      </c>
+      <c r="X23">
+        <v>12</v>
+      </c>
+      <c r="Y23">
+        <v>14</v>
+      </c>
+      <c r="Z23">
+        <v>13.5</v>
+      </c>
+      <c r="AA23">
+        <v>13</v>
+      </c>
+      <c r="AH23" s="20"/>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="19">
+        <v>53</v>
+      </c>
+      <c r="C24">
+        <v>21.5</v>
+      </c>
+      <c r="D24">
+        <v>19.5</v>
+      </c>
+      <c r="E24">
+        <v>13.4</v>
+      </c>
+      <c r="F24">
+        <v>18</v>
+      </c>
+      <c r="G24">
+        <v>14.5</v>
+      </c>
+      <c r="M24">
+        <v>15.5</v>
+      </c>
+      <c r="N24">
+        <v>21.5</v>
+      </c>
+      <c r="O24">
+        <v>17.5</v>
+      </c>
+      <c r="P24">
+        <v>18.2</v>
+      </c>
+      <c r="Q24">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="W24">
+        <v>20</v>
+      </c>
+      <c r="X24">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="Y24">
+        <v>15</v>
+      </c>
+      <c r="Z24">
+        <v>18.5</v>
+      </c>
+      <c r="AA24">
+        <v>13</v>
+      </c>
+      <c r="AH24" s="20"/>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>11</v>
+      </c>
+      <c r="F25">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G25">
+        <v>13</v>
+      </c>
+      <c r="M25">
+        <v>16.5</v>
+      </c>
+      <c r="N25">
+        <v>13</v>
+      </c>
+      <c r="O25">
+        <v>12</v>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+      <c r="Q25">
+        <v>11.5</v>
+      </c>
+      <c r="W25">
+        <v>11</v>
+      </c>
+      <c r="X25">
+        <v>14.2</v>
+      </c>
+      <c r="Y25">
+        <v>12</v>
+      </c>
+      <c r="Z25">
+        <v>15</v>
+      </c>
+      <c r="AA25">
+        <v>14</v>
+      </c>
+      <c r="AH25" s="20"/>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="19">
+        <v>58</v>
+      </c>
+      <c r="C26">
+        <v>21</v>
+      </c>
+      <c r="D26">
+        <v>17.2</v>
+      </c>
+      <c r="E26">
+        <v>16.5</v>
+      </c>
+      <c r="F26">
+        <v>15.5</v>
+      </c>
+      <c r="G26">
+        <v>18.8</v>
+      </c>
+      <c r="M26">
+        <v>16.3</v>
+      </c>
+      <c r="N26">
+        <v>13.4</v>
+      </c>
+      <c r="O26">
+        <v>12.1</v>
+      </c>
+      <c r="P26">
+        <v>20.7</v>
+      </c>
+      <c r="Q26">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="W26">
+        <v>20</v>
+      </c>
+      <c r="X26">
+        <v>18</v>
+      </c>
+      <c r="Y26">
+        <v>14.5</v>
+      </c>
+      <c r="Z26">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AA26">
+        <v>19</v>
+      </c>
+      <c r="AH26" s="20"/>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27">
+        <v>12.5</v>
+      </c>
+      <c r="D27">
+        <v>18.5</v>
+      </c>
+      <c r="E27">
+        <v>15.4</v>
+      </c>
+      <c r="F27">
+        <v>16.3</v>
+      </c>
+      <c r="G27">
+        <v>12</v>
+      </c>
+      <c r="M27">
+        <v>14</v>
+      </c>
+      <c r="N27">
+        <v>10.5</v>
+      </c>
+      <c r="O27">
+        <v>10.3</v>
+      </c>
+      <c r="P27">
+        <v>12.8</v>
+      </c>
+      <c r="Q27">
+        <v>15</v>
+      </c>
+      <c r="W27">
+        <v>13</v>
+      </c>
+      <c r="X27">
+        <v>16</v>
+      </c>
+      <c r="Y27">
+        <v>14</v>
+      </c>
+      <c r="Z27">
+        <v>14.2</v>
+      </c>
+      <c r="AA27">
+        <v>13</v>
+      </c>
+      <c r="AH27" s="20"/>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="19">
+        <v>78</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>21</v>
+      </c>
+      <c r="E28">
+        <v>20</v>
+      </c>
+      <c r="F28">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>12</v>
+      </c>
+      <c r="M28">
+        <v>18</v>
+      </c>
+      <c r="N28">
+        <v>19</v>
+      </c>
+      <c r="O28">
+        <v>23</v>
+      </c>
+      <c r="P28">
+        <v>17</v>
+      </c>
+      <c r="Q28">
+        <v>18</v>
+      </c>
+      <c r="W28">
+        <v>10.5</v>
+      </c>
+      <c r="X28">
+        <v>20</v>
+      </c>
+      <c r="Y28">
+        <v>21</v>
+      </c>
+      <c r="Z28">
+        <v>15</v>
+      </c>
+      <c r="AA28">
+        <v>13.4</v>
+      </c>
+      <c r="AH28" s="20"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29">
+        <v>13</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>9</v>
+      </c>
+      <c r="M29">
+        <v>12</v>
+      </c>
+      <c r="N29">
+        <v>14</v>
+      </c>
+      <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
+        <v>17</v>
+      </c>
+      <c r="Q29">
+        <v>15</v>
+      </c>
+      <c r="W29">
+        <v>14</v>
+      </c>
+      <c r="X29">
+        <v>14</v>
+      </c>
+      <c r="Y29">
+        <v>11</v>
+      </c>
+      <c r="Z29">
+        <v>13</v>
+      </c>
+      <c r="AA29">
+        <v>12</v>
+      </c>
+      <c r="AH29" s="20"/>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="19">
+        <v>89</v>
+      </c>
+      <c r="C30">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>16.3</v>
+      </c>
+      <c r="E30">
+        <v>16.5</v>
+      </c>
+      <c r="F30">
+        <v>17</v>
+      </c>
+      <c r="G30">
+        <v>17.3</v>
+      </c>
+      <c r="M30">
+        <v>18.3</v>
+      </c>
+      <c r="N30">
+        <v>16.3</v>
+      </c>
+      <c r="O30">
+        <v>17</v>
+      </c>
+      <c r="P30">
+        <v>15.2</v>
+      </c>
+      <c r="Q30">
+        <v>18.2</v>
+      </c>
+      <c r="W30">
+        <v>14</v>
+      </c>
+      <c r="X30">
+        <v>17.5</v>
+      </c>
+      <c r="Y30">
+        <v>16</v>
+      </c>
+      <c r="Z30">
+        <v>15.5</v>
+      </c>
+      <c r="AA30">
+        <v>20</v>
+      </c>
+      <c r="AH30" s="20"/>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31">
+        <v>12.5</v>
+      </c>
+      <c r="D31">
+        <v>15.5</v>
+      </c>
+      <c r="E31">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>14.3</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>12.1</v>
+      </c>
+      <c r="N31">
+        <v>19</v>
+      </c>
+      <c r="O31">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="P31">
+        <v>14.1</v>
+      </c>
+      <c r="Q31">
+        <v>15.3</v>
+      </c>
+      <c r="W31">
+        <v>15</v>
+      </c>
+      <c r="X31">
+        <v>14.5</v>
+      </c>
+      <c r="Y31">
+        <v>15.8</v>
+      </c>
+      <c r="Z31">
+        <v>13.5</v>
+      </c>
+      <c r="AA31">
+        <v>12</v>
+      </c>
+      <c r="AH31" s="20"/>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="19">
+        <v>112</v>
+      </c>
+      <c r="C32">
+        <v>20.5</v>
+      </c>
+      <c r="D32">
+        <v>18</v>
+      </c>
+      <c r="E32">
+        <v>19.5</v>
+      </c>
+      <c r="F32">
+        <v>17</v>
+      </c>
+      <c r="G32">
+        <v>18.5</v>
+      </c>
+      <c r="M32">
+        <v>18</v>
+      </c>
+      <c r="N32">
+        <v>14</v>
+      </c>
+      <c r="O32">
+        <v>18.5</v>
+      </c>
+      <c r="P32">
+        <v>14.4</v>
+      </c>
+      <c r="Q32">
+        <v>13.3</v>
+      </c>
+      <c r="W32">
+        <v>19</v>
+      </c>
+      <c r="X32">
+        <v>17</v>
+      </c>
+      <c r="Y32">
+        <v>18.2</v>
+      </c>
+      <c r="Z32">
+        <v>16</v>
+      </c>
+      <c r="AA32">
+        <v>15</v>
+      </c>
+      <c r="AH32" s="20"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <v>17.3</v>
+      </c>
+      <c r="E33">
+        <v>14.5</v>
+      </c>
+      <c r="F33">
+        <v>16</v>
+      </c>
+      <c r="G33">
+        <v>16.5</v>
+      </c>
+      <c r="M33">
+        <v>15.4</v>
+      </c>
+      <c r="N33">
+        <v>13.5</v>
+      </c>
+      <c r="O33">
+        <v>17.5</v>
+      </c>
+      <c r="P33">
+        <v>9.5</v>
+      </c>
+      <c r="Q33">
+        <v>14.2</v>
+      </c>
+      <c r="W33">
+        <v>13.4</v>
+      </c>
+      <c r="X33">
+        <v>15</v>
+      </c>
+      <c r="Y33">
+        <v>16</v>
+      </c>
+      <c r="Z33">
+        <v>12</v>
+      </c>
+      <c r="AA33">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="M2:V2"/>
+    <mergeCell ref="C1:V1"/>
+    <mergeCell ref="W2:AF2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
       <c r="L1" s="13" t="s">
         <v>116</v>
       </c>
